--- a/Input/StatusTrackerExcel_07_05_2025_14_02_36.xlsx
+++ b/Input/StatusTrackerExcel_07_05_2025_14_02_36.xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="BOTStatus_TrackerDetailed" sheetId="1" r:id="rId1"/>
-    <sheet name="BOTStatus_Tracker1" sheetId="2" r:id="rId2"/>
-    <sheet name="EndReport_Tracker" sheetId="3" r:id="rId3"/>
+    <sheet name="ClaimRunSummary" sheetId="1" r:id="rId1"/>
+    <sheet name="BotRunTracker" sheetId="2" r:id="rId2"/>
+    <sheet name="EmailSummary" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
